--- a/nexo_os/data/synthetic/broken/bad_enum.xlsx
+++ b/nexo_os/data/synthetic/broken/bad_enum.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POL-EXP-15</t>
+          <t>POL-A1-a</t>
         </is>
       </c>
       <c r="C7" t="n">
